--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58067</v>
+        <v>58122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1339,11 +1339,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 62483-2021 artfynd.xlsx
+++ b/artfynd/A 62483-2021 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>115268225</v>
       </c>
       <c r="B7" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
